--- a/cable/cable_db.xlsx
+++ b/cable/cable_db.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mario\python\pypacity\cable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F3E0B6-3A7D-4D39-B359-7F6AEEE9605C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239A288F-B9CD-4562-82A6-73600CA20A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29780" yWindow="980" windowWidth="14400" windowHeight="7190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24705" yWindow="1680" windowWidth="21600" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Cstring</t>
   </si>
@@ -64,6 +64,18 @@
   </si>
   <si>
     <t>400 mm2 DRAKE 26/7 ACSR</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>4.44</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>10.4</t>
   </si>
 </sst>
 </file>
@@ -381,13 +393,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="23.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -395,71 +407,83 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2">
         <v>28.12</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2">
         <v>25</v>
       </c>
-      <c r="D2">
+      <c r="F2">
         <v>75</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>100</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>7.2840000000000002E-2</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>8.6889999999999995E-2</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>0.5</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>0.5</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>3</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>1139.5</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>351.7</v>
       </c>
     </row>

--- a/cable/cable_db.xlsx
+++ b/cable/cable_db.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mario\python\pypacity\cable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239A288F-B9CD-4562-82A6-73600CA20A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257EE18E-E249-4CEE-BF59-99068BEFC324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24705" yWindow="1680" windowWidth="21600" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26925" yWindow="2055" windowWidth="28170" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Cstring</t>
   </si>
@@ -76,6 +76,12 @@
   </si>
   <si>
     <t>10.4</t>
+  </si>
+  <si>
+    <t>TotalS</t>
+  </si>
+  <si>
+    <t>28.12</t>
   </si>
 </sst>
 </file>
@@ -393,13 +399,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="23.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -442,13 +448,16 @@
       <c r="N1" t="s">
         <v>11</v>
       </c>
+      <c r="O1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2">
-        <v>28.12</v>
+      <c r="B2" t="s">
+        <v>18</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -485,6 +494,9 @@
       </c>
       <c r="N2">
         <v>351.7</v>
+      </c>
+      <c r="O2">
+        <v>486.6</v>
       </c>
     </row>
   </sheetData>

--- a/cable/cable_db.xlsx
+++ b/cable/cable_db.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mario\python\pypacity\cable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257EE18E-E249-4CEE-BF59-99068BEFC324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E9B122-2DB3-473C-AFC8-594310EC0838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26925" yWindow="2055" windowWidth="28170" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1260" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>Cstring</t>
   </si>
@@ -72,16 +83,70 @@
     <t>4.44</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>10.4</t>
-  </si>
-  <si>
     <t>TotalS</t>
   </si>
   <si>
     <t>28.12</t>
+  </si>
+  <si>
+    <t>17.50</t>
+  </si>
+  <si>
+    <t>21.80</t>
+  </si>
+  <si>
+    <t>2.50</t>
+  </si>
+  <si>
+    <t>3.44</t>
+  </si>
+  <si>
+    <t>0.21993</t>
+  </si>
+  <si>
+    <t>0.07284</t>
+  </si>
+  <si>
+    <t>0.08689</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>1139.5</t>
+  </si>
+  <si>
+    <t>351.7</t>
+  </si>
+  <si>
+    <t>486.6</t>
+  </si>
+  <si>
+    <t>0.25197</t>
+  </si>
+  <si>
+    <t>0.13384</t>
+  </si>
+  <si>
+    <t>0.15707</t>
+  </si>
+  <si>
+    <t>379.81</t>
+  </si>
+  <si>
+    <t>128.16</t>
+  </si>
+  <si>
+    <t>623.22</t>
+  </si>
+  <si>
+    <t>147.22</t>
+  </si>
+  <si>
+    <t>LA-180</t>
+  </si>
+  <si>
+    <t>LA-280</t>
   </si>
 </sst>
 </file>
@@ -399,13 +464,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="23.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -413,90 +478,166 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>25</v>
+      </c>
+      <c r="E2">
+        <v>75</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>85</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>25</v>
-      </c>
-      <c r="F2">
-        <v>75</v>
-      </c>
-      <c r="G2">
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>85</v>
+      </c>
+      <c r="F4">
         <v>100</v>
       </c>
-      <c r="H2">
-        <v>7.2840000000000002E-2</v>
-      </c>
-      <c r="I2">
-        <v>8.6889999999999995E-2</v>
-      </c>
-      <c r="J2">
-        <v>0.5</v>
-      </c>
-      <c r="K2">
-        <v>0.5</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>1139.5</v>
-      </c>
-      <c r="N2">
-        <v>351.7</v>
-      </c>
-      <c r="O2">
-        <v>486.6</v>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/cable/cable_db.xlsx
+++ b/cable/cable_db.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mario\python\pypacity\cable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E9B122-2DB3-473C-AFC8-594310EC0838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3EB68F0-CF1D-4E7A-920B-568A622E0757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1260" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
   <si>
     <t>Cstring</t>
   </si>
@@ -147,6 +145,66 @@
   </si>
   <si>
     <t>LA-280</t>
+  </si>
+  <si>
+    <t>HERON</t>
+  </si>
+  <si>
+    <t>22.96</t>
+  </si>
+  <si>
+    <t>3.60</t>
+  </si>
+  <si>
+    <t>623.00</t>
+  </si>
+  <si>
+    <t>147.00</t>
+  </si>
+  <si>
+    <t>LA-455</t>
+  </si>
+  <si>
+    <t>27.72</t>
+  </si>
+  <si>
+    <t>4.00</t>
+  </si>
+  <si>
+    <t>971.40</t>
+  </si>
+  <si>
+    <t>220.00</t>
+  </si>
+  <si>
+    <t>0.1122</t>
+  </si>
+  <si>
+    <t>0.1507</t>
+  </si>
+  <si>
+    <t>0.0675</t>
+  </si>
+  <si>
+    <t>0.0906</t>
+  </si>
+  <si>
+    <t>10.4</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>8.04</t>
+  </si>
+  <si>
+    <t>8.61</t>
+  </si>
+  <si>
+    <t>9.24</t>
+  </si>
+  <si>
+    <t>D1</t>
   </si>
 </sst>
 </file>
@@ -464,13 +522,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.59765625" customWidth="1"/>
+    <col min="4" max="4" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -478,43 +549,46 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -522,43 +596,46 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>25</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>75</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>100</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
-        <v>24</v>
-      </c>
       <c r="J2" t="s">
         <v>24</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2">
         <v>3</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>26</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -566,40 +643,43 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>85</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>100</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>28</v>
       </c>
-      <c r="I3" t="s">
-        <v>24</v>
-      </c>
       <c r="J3" t="s">
         <v>24</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3">
         <v>2</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>31</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -607,37 +687,128 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>85</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>100</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>30</v>
       </c>
-      <c r="I4" t="s">
-        <v>24</v>
-      </c>
       <c r="J4" t="s">
         <v>24</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
         <v>2</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>33</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>85</v>
+      </c>
+      <c r="G5">
+        <v>100</v>
+      </c>
+      <c r="H5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>85</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/cable/cable_db.xlsx
+++ b/cable/cable_db.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mario\python\pypacity\cable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3EB68F0-CF1D-4E7A-920B-568A622E0757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836FF880-31B5-436A-9F29-BA474DFFFE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -220,12 +223,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -240,8 +249,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,25 +533,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="24.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.59765625" customWidth="1"/>
-    <col min="4" max="4" width="4.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.578125" customWidth="1"/>
+    <col min="4" max="4" width="4.578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.26171875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.83984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.26171875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.1015625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.26171875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.26171875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.41796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -588,7 +598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -635,7 +645,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -679,7 +689,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -723,51 +733,51 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+    <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>5</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>85</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>100</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5">
+      <c r="J5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="1">
         <v>3</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>42</v>
       </c>
